--- a/2083_2084/estimate/budget maag estimate/पाङ्ग्रेबास मेलडाँडा सडक/पाङ्ग्रेबास मेलडाँडा सडक.xlsx
+++ b/2083_2084/estimate/budget maag estimate/पाङ्ग्रेबास मेलडाँडा सडक/पाङ्ग्रेबास मेलडाँडा सडक.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481BF658-D44A-46EE-96B4-7FF2BF2250BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B87508-F5B6-42A3-88DC-1DA41ACA5043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="14" r:id="rId1"/>
@@ -57,8 +57,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -66,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="51">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -243,14 +241,55 @@
       <t xml:space="preserve">d]n8fF8f ;8s </t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Project:-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>nfdf la;f}gf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve">d]n8fF8f lj;/fd] ;8s </t>
+    </r>
+  </si>
+  <si>
+    <t>Date: 208306/26</t>
+  </si>
+  <si>
+    <t>-for masonry wall</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -420,9 +459,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -434,7 +473,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -458,14 +497,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -484,7 +523,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -499,7 +538,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -520,7 +559,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -542,6 +581,12 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -553,12 +598,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1093,116 +1132,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+    </row>
+    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>30</v>
       </c>
@@ -1213,13 +1252,13 @@
       <c r="F7" s="42"/>
       <c r="G7" s="11"/>
       <c r="H7" s="43" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I7" s="43"/>
       <c r="J7" s="43"/>
       <c r="K7" s="43"/>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -1254,7 +1293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -1271,10 +1310,10 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C10" s="37">
         <v>0.5</v>
@@ -1285,14 +1324,14 @@
       </c>
       <c r="E10" s="33">
         <f>E15</f>
-        <v>1.1429442243218531</v>
+        <v>1.2191405059433098</v>
       </c>
       <c r="F10" s="33">
         <v>0.6</v>
       </c>
       <c r="G10" s="33">
         <f>PRODUCT(C10:F10)</f>
-        <v>1.3715330691862235</v>
+        <v>1.4629686071319716</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -1312,7 +1351,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32" t="s">
         <v>32</v>
@@ -1321,7 +1360,7 @@
         <v>0.5</v>
       </c>
       <c r="D11" s="33">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="E11" s="33">
         <v>0.9</v>
@@ -1332,7 +1371,7 @@
       </c>
       <c r="G11" s="33">
         <f>PRODUCT(C11:F11)</f>
-        <v>44.931423346540683</v>
+        <v>21.663364827796403</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -1343,7 +1382,7 @@
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="34" t="s">
         <v>16</v>
@@ -1354,7 +1393,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <f>SUM(G10:G11)</f>
-        <v>46.302956415726904</v>
+        <v>23.126333434928377</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>17</v>
@@ -1364,11 +1403,11 @@
       </c>
       <c r="J12" s="18">
         <f>G12*I12</f>
-        <v>3420.8624199939036</v>
+        <v>1708.5735141725083</v>
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1381,7 +1420,7 @@
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>2</v>
       </c>
@@ -1398,11 +1437,11 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="32" t="str">
         <f>B10</f>
-        <v>-for masory wall</v>
+        <v>-for masonry wall</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -1413,14 +1452,14 @@
       </c>
       <c r="E15" s="33">
         <f>E21</f>
-        <v>1.1429442243218531</v>
+        <v>1.2191405059433098</v>
       </c>
       <c r="F15" s="33">
         <v>0.15</v>
       </c>
       <c r="G15" s="33">
         <f>PRODUCT(C15:F15)</f>
-        <v>0.68576653459311177</v>
+        <v>0.73148430356598582</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -1440,7 +1479,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="32" t="str">
         <f>B11</f>
@@ -1451,7 +1490,7 @@
       </c>
       <c r="D16" s="33">
         <f>D11</f>
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="E16" s="33">
         <f>E11</f>
@@ -1462,7 +1501,7 @@
       </c>
       <c r="G16" s="33">
         <f>PRODUCT(C16:F16)</f>
-        <v>37.799999999999997</v>
+        <v>18.224999999999998</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -1473,7 +1512,7 @@
       <c r="O16" s="36"/>
       <c r="P16" s="36"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="32" t="s">
         <v>39</v>
@@ -1503,7 +1542,7 @@
       <c r="O17" s="36"/>
       <c r="P17" s="36"/>
     </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="34" t="s">
         <v>16</v>
@@ -1514,7 +1553,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <f>SUM(G15:G17)</f>
-        <v>38.570141534593112</v>
+        <v>19.040859303565984</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>17</v>
@@ -1524,11 +1563,11 @@
       </c>
       <c r="J18" s="18">
         <f>G18*I18</f>
-        <v>179204.20589661115</v>
+        <v>88467.450087635225</v>
       </c>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -1541,7 +1580,7 @@
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>3</v>
       </c>
@@ -1558,11 +1597,11 @@
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="32" t="str">
         <f>B15</f>
-        <v>-for masory wall</v>
+        <v>-for masonry wall</v>
       </c>
       <c r="C21" s="17">
         <v>1</v>
@@ -1573,14 +1612,14 @@
       </c>
       <c r="E21" s="33">
         <f>F32/2</f>
-        <v>1.1429442243218531</v>
+        <v>1.2191405059433098</v>
       </c>
       <c r="F21" s="33">
         <v>0.05</v>
       </c>
       <c r="G21" s="33">
         <f>PRODUCT(C21:F21)</f>
-        <v>0.22858884486437062</v>
+        <v>0.24382810118866197</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -1600,7 +1639,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="32" t="str">
         <f>B16</f>
@@ -1612,18 +1651,18 @@
       </c>
       <c r="D22" s="33">
         <f t="shared" si="0"/>
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="F22" s="33">
-        <v>0.1</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G22" s="33">
         <f>PRODUCT(C22:F22)</f>
-        <v>25.200000000000003</v>
+        <v>9.1124999999999989</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -1634,7 +1673,7 @@
       <c r="O22" s="36"/>
       <c r="P22" s="36"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="32" t="str">
         <f>B17</f>
@@ -1668,7 +1707,7 @@
       <c r="O23" s="36"/>
       <c r="P23" s="36"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="34" t="s">
         <v>16</v>
@@ -1679,7 +1718,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <f>SUM(G21:G23)</f>
-        <v>25.470776344864372</v>
+        <v>9.3985156011886613</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>17</v>
@@ -1689,11 +1728,11 @@
       </c>
       <c r="J24" s="18">
         <f>G24*I24</f>
-        <v>292925.89923082234</v>
+        <v>108087.34671600215</v>
       </c>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -1706,7 +1745,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:16" ht="156" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>4</v>
       </c>
@@ -1723,7 +1762,7 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="32" t="str">
         <f>B22</f>
@@ -1735,7 +1774,7 @@
       </c>
       <c r="D27" s="33">
         <f>D22</f>
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="E27" s="33">
         <v>0.3</v>
@@ -1746,7 +1785,7 @@
       </c>
       <c r="G27" s="33">
         <f>PRODUCT(C27:F27)</f>
-        <v>59.908564462054251</v>
+        <v>28.88448643706187</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -1757,7 +1796,7 @@
       <c r="O27" s="36"/>
       <c r="P27" s="36"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="32" t="str">
         <f>B23</f>
@@ -1791,7 +1830,7 @@
       <c r="O28" s="36"/>
       <c r="P28" s="36"/>
     </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="34" t="s">
         <v>16</v>
@@ -1802,7 +1841,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <f>SUM(G27:G28)</f>
-        <v>60.357878695519659</v>
+        <v>29.333800670527278</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>17</v>
@@ -1812,11 +1851,11 @@
       </c>
       <c r="J29" s="18">
         <f>G29*I29</f>
-        <v>627294.00107345323</v>
+        <v>304863.55032672966</v>
       </c>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -1829,9 +1868,9 @@
       <c r="J30" s="17"/>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>35</v>
@@ -1846,11 +1885,11 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="32" t="str">
         <f>B21</f>
-        <v>-for masory wall</v>
+        <v>-for masonry wall</v>
       </c>
       <c r="C32" s="17">
         <v>1</v>
@@ -1860,15 +1899,15 @@
       </c>
       <c r="E32" s="33">
         <f>((F32/2)+0.45)/2</f>
-        <v>0.7964721121609265</v>
+        <v>0.83457025297165488</v>
       </c>
       <c r="F32" s="33">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
       </c>
       <c r="G32" s="33">
         <f>PRODUCT(C32:F32)</f>
-        <v>7.2825856034220644</v>
+        <v>8.1396672036247946</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
@@ -1888,7 +1927,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="32" t="s">
         <v>38</v>
@@ -1898,7 +1937,7 @@
       </c>
       <c r="D33" s="33">
         <f>E32</f>
-        <v>0.7964721121609265</v>
+        <v>0.83457025297165488</v>
       </c>
       <c r="E33" s="33">
         <v>0.45</v>
@@ -1908,7 +1947,7 @@
       </c>
       <c r="G33" s="33">
         <f>C33*D33*(E33*F33*PI())/4</f>
-        <v>-0.12667341615291683</v>
+        <v>-0.13273266364179154</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
@@ -1919,7 +1958,7 @@
       <c r="O33" s="36"/>
       <c r="P33" s="36"/>
     </row>
-    <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="34" t="s">
         <v>16</v>
@@ -1930,7 +1969,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <f>SUM(G32:G33)</f>
-        <v>7.1559121872691476</v>
+        <v>8.0069345399830034</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
@@ -1940,11 +1979,11 @@
       </c>
       <c r="J34" s="18">
         <f>G34*I34</f>
-        <v>68172.586430066352</v>
+        <v>76280.063628783071</v>
       </c>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -1957,9 +1996,9 @@
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>33</v>
@@ -1986,7 +2025,7 @@
       </c>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="8"/>
       <c r="C37" s="3"/>
@@ -1999,9 +2038,9 @@
       <c r="J37" s="18"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>18</v>
@@ -2028,7 +2067,7 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="8"/>
       <c r="C39" s="3"/>
@@ -2041,7 +2080,7 @@
       <c r="J39" s="18"/>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="21"/>
       <c r="B40" s="22" t="s">
         <v>21</v>
@@ -2055,11 +2094,11 @@
       <c r="I40" s="18"/>
       <c r="J40" s="18">
         <f>SUM(J9:J38)</f>
-        <v>1176517.5550509468</v>
+        <v>584906.98427332263</v>
       </c>
       <c r="K40" s="25"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
       <c r="O41" s="20"/>
@@ -2068,14 +2107,14 @@
       <c r="R41" s="20"/>
       <c r="S41" s="20"/>
     </row>
-    <row r="42" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26"/>
       <c r="B42" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="40">
         <f>J40</f>
-        <v>1176517.5550509468</v>
+        <v>584906.98427332263</v>
       </c>
       <c r="D42" s="41"/>
       <c r="E42" s="9">
@@ -2095,64 +2134,64 @@
       <c r="R42" s="19"/>
       <c r="S42" s="19"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B43" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C43" s="44">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="D43" s="45"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B44" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="44">
         <f>C43-C46-C47</f>
-        <v>950000</v>
+        <v>475000</v>
       </c>
       <c r="D44" s="45"/>
       <c r="E44" s="9">
         <f>C44/C42*100</f>
-        <v>80.74677644388079</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+        <v>81.209493606941791</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B45" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C45" s="46">
         <f>C42-C44</f>
-        <v>226517.55505094677</v>
+        <v>109906.98427332263</v>
       </c>
       <c r="D45" s="46"/>
       <c r="E45" s="9">
         <f>100-E44</f>
-        <v>19.25322355611921</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+        <v>18.790506393058209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B46" s="27" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="40">
         <f>C43*0.03</f>
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="D46" s="41"/>
       <c r="E46" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B47" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C47" s="40">
         <f>C43*0.02</f>
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D47" s="41"/>
       <c r="E47" s="9">
@@ -2191,116 +2230,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E757301F-B804-40B2-A270-FAABD2C2A0EC}">
   <dimension ref="A1:S56"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="19" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="19" customWidth="1"/>
     <col min="6" max="6" width="9" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="19" customWidth="1"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+    </row>
+    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>30</v>
       </c>
@@ -2317,7 +2356,7 @@
       <c r="J7" s="43"/>
       <c r="K7" s="43"/>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -2352,7 +2391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -2369,7 +2408,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
         <v>36</v>
@@ -2410,7 +2449,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32" t="s">
         <v>32</v>
@@ -2441,7 +2480,7 @@
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="34" t="s">
         <v>16</v>
@@ -2466,7 +2505,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -2479,7 +2518,7 @@
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>2</v>
       </c>
@@ -2496,7 +2535,7 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="32" t="str">
         <f>B10</f>
@@ -2538,7 +2577,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="32" t="str">
         <f>B11</f>
@@ -2571,7 +2610,7 @@
       <c r="O16" s="36"/>
       <c r="P16" s="36"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="32" t="s">
         <v>39</v>
@@ -2601,7 +2640,7 @@
       <c r="O17" s="36"/>
       <c r="P17" s="36"/>
     </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="34" t="s">
         <v>16</v>
@@ -2626,7 +2665,7 @@
       </c>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -2639,7 +2678,7 @@
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>3</v>
       </c>
@@ -2656,7 +2695,7 @@
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="32" t="str">
         <f>B15</f>
@@ -2698,7 +2737,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="32" t="str">
         <f>B16</f>
@@ -2732,7 +2771,7 @@
       <c r="O22" s="36"/>
       <c r="P22" s="36"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="32" t="str">
         <f>B17</f>
@@ -2766,7 +2805,7 @@
       <c r="O23" s="36"/>
       <c r="P23" s="36"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="34" t="s">
         <v>16</v>
@@ -2791,7 +2830,7 @@
       </c>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -2804,7 +2843,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:16" ht="156" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>4</v>
       </c>
@@ -2821,7 +2860,7 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="32" t="str">
         <f>B22</f>
@@ -2855,7 +2894,7 @@
       <c r="O27" s="36"/>
       <c r="P27" s="36"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="32" t="str">
         <f>B23</f>
@@ -2889,7 +2928,7 @@
       <c r="O28" s="36"/>
       <c r="P28" s="36"/>
     </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="34" t="s">
         <v>16</v>
@@ -2914,7 +2953,7 @@
       </c>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -2927,7 +2966,7 @@
       <c r="J30" s="17"/>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>5</v>
       </c>
@@ -2944,7 +2983,7 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="32" t="str">
         <f>B21</f>
@@ -2986,7 +3025,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="32" t="s">
         <v>38</v>
@@ -3017,7 +3056,7 @@
       <c r="O33" s="36"/>
       <c r="P33" s="36"/>
     </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="34" t="s">
         <v>16</v>
@@ -3042,7 +3081,7 @@
       </c>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -3055,7 +3094,7 @@
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>6</v>
       </c>
@@ -3072,7 +3111,7 @@
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
         <v>41</v>
@@ -3113,7 +3152,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="34" t="s">
         <v>16</v>
@@ -3138,7 +3177,7 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -3151,7 +3190,7 @@
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:16" ht="78" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>7</v>
       </c>
@@ -3176,7 +3215,7 @@
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="32" t="str">
         <f>B37</f>
@@ -3220,7 +3259,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="32"/>
       <c r="C42" s="37">
@@ -3252,7 +3291,7 @@
       <c r="O42" s="36"/>
       <c r="P42" s="36"/>
     </row>
-    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
         <v>16</v>
@@ -3277,7 +3316,7 @@
       </c>
       <c r="K43" s="5"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -3290,7 +3329,7 @@
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>8</v>
       </c>
@@ -3319,7 +3358,7 @@
       </c>
       <c r="K45" s="5"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="8"/>
       <c r="C46" s="3"/>
@@ -3332,7 +3371,7 @@
       <c r="J46" s="18"/>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>9</v>
       </c>
@@ -3361,7 +3400,7 @@
       </c>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="8"/>
       <c r="C48" s="3"/>
@@ -3374,7 +3413,7 @@
       <c r="J48" s="18"/>
       <c r="K48" s="5"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="22" t="s">
         <v>21</v>
@@ -3392,7 +3431,7 @@
       </c>
       <c r="K49" s="25"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M50" s="20"/>
       <c r="N50" s="20"/>
       <c r="O50" s="20"/>
@@ -3401,7 +3440,7 @@
       <c r="R50" s="20"/>
       <c r="S50" s="20"/>
     </row>
-    <row r="51" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26"/>
       <c r="B51" s="27" t="s">
         <v>20</v>
@@ -3428,7 +3467,7 @@
       <c r="R51" s="19"/>
       <c r="S51" s="19"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B52" s="27" t="s">
         <v>22</v>
       </c>
@@ -3438,7 +3477,7 @@
       <c r="D52" s="45"/>
       <c r="E52" s="9"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B53" s="27" t="s">
         <v>23</v>
       </c>
@@ -3452,7 +3491,7 @@
         <v>80.093430687563028</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B54" s="27" t="s">
         <v>29</v>
       </c>
@@ -3466,7 +3505,7 @@
         <v>19.906569312436972</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B55" s="27" t="s">
         <v>24</v>
       </c>
@@ -3479,7 +3518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B56" s="27" t="s">
         <v>25</v>
       </c>
